--- a/suppliers_import_template.xlsx
+++ b/suppliers_import_template.xlsx
@@ -5,22 +5,35 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\software\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FBD1A7-7C62-400A-A90B-0DF3DF199718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC0DEF5-0B57-426E-8831-C49FF3892061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Suppliers" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
   <si>
     <t>Name</t>
   </si>
@@ -53,15 +66,6 @@
   </si>
   <si>
     <t>Contact Email</t>
-  </si>
-  <si>
-    <t>Li Wei</t>
-  </si>
-  <si>
-    <t>+86 123 456 7890</t>
-  </si>
-  <si>
-    <t>contact@example.com</t>
   </si>
   <si>
     <t>ZHEJIANG FUSHENGDA TECHNOLOGY CO., LTD</t>
@@ -148,28 +152,25 @@
 SUZHOU CITY, CHINA</t>
   </si>
   <si>
-    <t>jack</t>
-  </si>
-  <si>
-    <t>marcel</t>
-  </si>
-  <si>
-    <t>nick</t>
-  </si>
-  <si>
-    <t>tom</t>
-  </si>
-  <si>
-    <t>+86 123 456 7891</t>
-  </si>
-  <si>
-    <t>+86 123 456 7892</t>
-  </si>
-  <si>
-    <t>+86 123 456 7893</t>
-  </si>
-  <si>
-    <t>+86 123 456 7894</t>
+    <t>cynthia@jxfushengda.com</t>
+  </si>
+  <si>
+    <t>0573-89973513</t>
+  </si>
+  <si>
+    <t>DORRIS</t>
+  </si>
+  <si>
+    <t>358501400100008000</t>
+  </si>
+  <si>
+    <t>CINDY</t>
+  </si>
+  <si>
+    <t>1102022009914080000</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -236,7 +237,6 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -244,9 +244,10 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -586,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.5" bestFit="1" customWidth="1"/>
@@ -596,10 +597,11 @@
     <col min="6" max="6" width="22.75" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="63.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -634,189 +636,190 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="3">
+        <v>401385242799</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" t="str">
+        <f>CONCATENATE(N3, F3)</f>
+        <v>401385242799</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="3">
+        <v>144252621923</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="N4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O4" t="str">
+        <f t="shared" ref="O4:O6" si="0">CONCATENATE(N4, F4)</f>
+        <v>144252621923</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="4">
-        <v>3.58501400100008E+17</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="E5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="N5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O5" t="str">
+        <f t="shared" si="0"/>
+        <v>521-357160-838</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="N6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O6" t="str">
+        <f t="shared" si="0"/>
+        <v>1102022009914080000</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="4">
-        <v>401385242799</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="4">
-        <v>144252621923</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J4" t="s">
-        <v>46</v>
-      </c>
-      <c r="K4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J5" t="s">
-        <v>47</v>
-      </c>
-      <c r="K5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="6">
-        <v>1.10202200991408E+18</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6" t="s">
-        <v>48</v>
-      </c>
-      <c r="K6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E7" s="3"/>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E7" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K1 I2:K2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:K1 F2 F6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>